--- a/InputData/bldgs/BCEU/BAU Components Energy Use_old.xlsx
+++ b/InputData/bldgs/BCEU/BAU Components Energy Use_old.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\bldgs\BCEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\90. 개인 폴더\김효진\기타업무\EPS\확인요청_빌딩\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3C5792-18E8-4F45-88C0-067B1418A7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6311DAEA-9FC6-43EE-B9A2-91A0CDC8BEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="705" windowWidth="13455" windowHeight="19980" tabRatio="952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="5085" windowWidth="30240" windowHeight="15240" tabRatio="952" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -197,9 +197,6 @@
   <si>
     <t>Urban population rate</t>
     <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.index.go.kr/potal/main/EachDtlPageDetail.do?idx_cd=1200</t>
   </si>
   <si>
     <t>heating</t>
@@ -586,6 +583,10 @@
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.index.go.kr/potal/main/EachDtlPageDetail.do?idx_cd=1200</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -599,7 +600,7 @@
     <numFmt numFmtId="180" formatCode="0.E+00"/>
     <numFmt numFmtId="181" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -752,8 +753,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,6 +788,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2ECF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -973,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1044,6 +1059,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="19" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="19" fillId="6" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="18" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="18" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1077,6 +1104,2407 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>초기값 변경 후</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$1:$AG$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>electricity (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$2:$AG$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>129000000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>128085531122407</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>129221921053730.27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>130255696422160.11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>131297741993537.39</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>132348123929485.69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>133406908920921.58</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>134474164192288.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>135549957505827.27</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>136634357165873.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>137727432023200.88</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>138829251479386.48</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>139939885491221.58</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>141059404575151.34</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>142187879811752.56</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>143325382850246.59</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>144471985913048.56</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>145627761800352.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>146792783894755.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>147967126165913.81</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>149150863175241.13</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>150344070080643.06</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>151546822641288.22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>152759197222418.53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>153981270800197.88</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>155213120966599.47</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>156454825934332.25</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>157706464541806.91</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>158968116258141.38</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>160239861188206.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>161521780077712.16</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>162813954318333.84</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>coal (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$3:$AG$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>natural gas (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$4:$AG$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>59200000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58150486891512.766</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57974902110890.578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59134400153108.391</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60317088156170.563</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61523429919293.977</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62753898517679.859</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64008976488033.461</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>65289156017794.133</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>66594939138150.016</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67926837920913.016</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>69285374679331.273</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70671082172917.906</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>72084503816376.266</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>73526193892703.797</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>74996717770557.875</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>76496652125969.031</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>78026585168488.406</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>79587116871858.172</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>81178859209295.344</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>82802436393481.25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>84458485121350.875</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>86147654823777.891</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>87870607920253.453</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>89628020078658.531</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>91420580480231.703</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>93248992089836.344</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>95113971931633.078</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>97016251370265.734</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>98956576397671.047</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>100935707925624.47</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>102954422084136.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>petroleum diesel (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$5:$AG$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>1740000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1635011946079.1394</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1609349044937.332</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1532100290780.3401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1458559476822.8838</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1388548621935.3853</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1321898288082.4868</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1258447170254.5273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1198041706082.3101</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1140535704190.3591</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1085789990389.2218</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1033672070850.5391</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>984055811449.71313</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>936821132500.12683</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>891853718140.12073</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>849044739669.3949</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>808290592165.26392</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>769492643741.33118</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>732556996841.74719</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>697394260993.34326</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>663919336465.66272</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>632051208315.31091</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>601712750316.1759</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>572830538300.99939</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>545334672462.55139</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>519158608184.34888</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>494238994991.50012</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>470515523231.90808</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>447930778116.77649</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>426430100767.1712</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>405961455930.34698</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>386475306045.69031</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>heat (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$6:$AG$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>15100000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14511153872761.668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14617592654224.467</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14880709322000.508</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15148562089796.518</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15421236207412.855</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15698818459146.287</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15981397191410.92</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16269062340856.316</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16561905462991.73</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16860019761325.582</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17163500117029.443</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17472443119135.973</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17786947095280.422</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18107112142995.469</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18433040161569.387</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18764834884477.637</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19102601912398.234</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19446448746821.402</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19796484824264.188</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20152821551100.941</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20515572339020.758</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20884852641123.133</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21260779988663.348</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21643474028459.289</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22033056560971.555</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22429651579069.043</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>22833385307492.285</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>23244386243027.148</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>23662785195401.637</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24088715328918.867</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24522312204839.406</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>biomass (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$7:$AG$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>6267151983000.002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6688080101261.1963</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7174485926807.4648</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7497337793513.7998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7834717994221.9199</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8187280303961.9063</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8555707917640.1914</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8940714773934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9343046938761.0293</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9763484051005.2754</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10202840833300.512</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10661968670799.033</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11141757260984.988</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11643136337729.313</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12167077472927.131</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12714595959208.852</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13286752777373.248</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13884656652355.043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14509466201711.02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>15162392180788.014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15844699828923.473</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16557711321225.027</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17302808330680.152</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>18081434705560.758</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18895099267310.992</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>19745378734339.984</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>20633920777385.281</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>21562447212367.617</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22532757336924.16</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>23546731417085.746</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24606334330854.602</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>25713619375743.059</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>kerosene (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$8:$AG$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>31500000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29616860228748.609</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29151998453271.219</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27752702527514.199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26420572806193.516</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25152385311496.227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23945070816544.406</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22795707417350.273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21701513461317.461</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20659840815174.223</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19668168456045.859</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18724096370155.656</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17825339744388.184</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16969723436657.551</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16155176711697.988</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15379728229536.484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14641501274518.732</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13938709213341.832</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13269651171101.424</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12632707914888.555</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12026337934973.904</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11449073714095.156</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10899518175818.588</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10376341303379.295</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9878276920817.0879</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9404119628617.8672</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8952721886444.209</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8522991235894.8867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8113887656571.9316</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7724421049056.4785</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7353648838701.7676</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7000673694444.082</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>heavy or residual fuel oil (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$9:$AG$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>3900000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3658245906752.4121</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3600826630225.0806</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3427986951974.2764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3263443578279.5107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3106798286522.0942</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2957671968769.0337</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2815703714268.1201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2680549935983.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2551883539056.0537</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2429393129181.3628</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2312782258980.6572</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2201768710549.5854</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2096083812443.2053</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1995471789445.9314</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1899689143552.5266</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1808504064662.0054</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1721695869558.229</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1639054467819.4338</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1560379853364.1008</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1485481620402.624</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1414178502623.2981</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1346297934497.3796</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1281675633641.5054</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1220155203226.7131</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1161587753471.8308</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1105831541305.1829</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1052751627322.5341</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1002219549211.0524</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>954113010848.92175</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>908315586328.17346</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>864716438184.42114</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LPG propane or butane (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$10:$AG$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>19000000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17835815247411.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17555866978791.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16713185363809.279</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15910952466346.434</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15147226747961.805</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14420159864059.637</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13727992190584.773</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13069048565436.703</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12441734234295.74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11844530991049.545</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11275993503479.166</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10734745815312.166</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10219478016177.182</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9728943071400.6758</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9261953803973.4434</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8817380021382.7168</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8394145780356.3457</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7991226782899.2412</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7607647897320.0771</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7242480798248.7129</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6894841719932.7744</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6563889317376.001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6248822630141.9531</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5948879143895.1387</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5663332944988.1719</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5391492963628.7393</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5132701301374.5596</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4886331638908.5801</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4651787720240.9678</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4428501909669.4014</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4215933818005.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>hydrogen (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$11:$AG$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="558921519"/>
+        <c:axId val="558922959"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="558921519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="558922959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="558922959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="558921519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1411100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>15689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>104215</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>91889</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A5E4BC0-2CF2-A2B6-EDAB-E07F67358918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1481,14 +3909,14 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="10"/>
     </row>
@@ -1511,7 +3939,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1585,7 +4013,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" s="10">
         <v>39.683100000000003</v>
@@ -1653,8 +4081,8 @@
       <c r="B37" s="14">
         <v>0.91800000000000004</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>36</v>
+      <c r="C37" s="33" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1694,9 +4122,10 @@
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{E3D81ACC-CD3F-44CE-83E2-D8AE4FA810A2}"/>
     <hyperlink ref="B14" r:id="rId2" xr:uid="{33897A44-3821-4B6E-8927-AA2917681289}"/>
+    <hyperlink ref="C37" r:id="rId3" xr:uid="{7D2E10FF-A52A-4B4D-B3F1-4EB000345C4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -1711,12 +4140,12 @@
   <sheetData>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -3169,7 +5598,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -4622,7 +7051,7 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -6075,7 +8504,7 @@
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -7528,7 +9957,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -8981,7 +11410,7 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -23541,44 +25970,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED6D3F1-92E7-40E9-A07E-C7DBA9C24A0B}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36">
+      <c r="B2" s="44">
         <v>129000000000000</v>
       </c>
       <c r="C2" s="36">
@@ -23597,11 +26027,11 @@
         <v>68100000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="44">
         <v>0</v>
       </c>
       <c r="C3" s="36">
@@ -23619,12 +26049,14 @@
       <c r="G3" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3" s="36"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="44">
         <v>59200000000000</v>
       </c>
       <c r="C4" s="36">
@@ -23642,12 +26074,14 @@
       <c r="G4" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4" s="36"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="44">
         <v>1740000000000</v>
       </c>
       <c r="C5" s="36">
@@ -23666,11 +26100,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="44">
         <v>15100000000000</v>
       </c>
       <c r="C6" s="36">
@@ -23689,12 +26123,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36">
-        <v>42700000000000</v>
+      <c r="B7" s="45">
+        <v>6267151983000.002</v>
       </c>
       <c r="C7" s="36">
         <v>208000000000</v>
@@ -23711,12 +26145,13 @@
       <c r="G7" s="36">
         <v>139000000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="44">
         <v>31500000000000</v>
       </c>
       <c r="C8" s="36">
@@ -23735,11 +26170,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="44">
         <v>3900000000000</v>
       </c>
       <c r="C9" s="36">
@@ -23758,11 +26193,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="44">
         <v>19000000000000</v>
       </c>
       <c r="C10" s="36">
@@ -23781,11 +26216,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="44">
         <v>0</v>
       </c>
       <c r="C11" s="36">
@@ -23804,33 +26239,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -23853,7 +26288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -23876,7 +26311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
@@ -24062,25 +26497,25 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -25781,10 +28216,10 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
-    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="32" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="32" width="10.25" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26556,137 +28991,137 @@
         <v>24522312204839.406</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="39">
         <f>Commercial_calculation!B9</f>
-        <v>42700000000000</v>
-      </c>
-      <c r="C7" s="3">
+        <v>6267151983000.002</v>
+      </c>
+      <c r="C7" s="39">
         <f>Commercial_calculation!C9</f>
-        <v>45560446860313.336</v>
-      </c>
-      <c r="D7" s="3">
+        <v>6688080101261.1963</v>
+      </c>
+      <c r="D7" s="39">
         <f>Commercial_calculation!D9</f>
-        <v>48873933904699.766</v>
-      </c>
-      <c r="E7" s="3">
+        <v>7174485926807.4648</v>
+      </c>
+      <c r="E7" s="39">
         <f>Commercial_calculation!E9</f>
-        <v>51073260930411.25</v>
-      </c>
-      <c r="F7" s="3">
+        <v>7497337793513.7998</v>
+      </c>
+      <c r="F7" s="39">
         <f>Commercial_calculation!F9</f>
-        <v>53371557672279.75</v>
-      </c>
-      <c r="G7" s="3">
+        <v>7834717994221.9199</v>
+      </c>
+      <c r="G7" s="39">
         <f>Commercial_calculation!G9</f>
-        <v>55773277767532.336</v>
-      </c>
-      <c r="H7" s="3">
+        <v>8187280303961.9063</v>
+      </c>
+      <c r="H7" s="39">
         <f>Commercial_calculation!H9</f>
-        <v>58283075267071.289</v>
-      </c>
-      <c r="I7" s="3">
+        <v>8555707917640.1914</v>
+      </c>
+      <c r="I7" s="39">
         <f>Commercial_calculation!I9</f>
-        <v>60905813654089.492</v>
-      </c>
-      <c r="J7" s="3">
+        <v>8940714773934</v>
+      </c>
+      <c r="J7" s="39">
         <f>Commercial_calculation!J9</f>
-        <v>63646575268523.516</v>
-      </c>
-      <c r="K7" s="3">
+        <v>9343046938761.0293</v>
+      </c>
+      <c r="K7" s="39">
         <f>Commercial_calculation!K9</f>
-        <v>66510671155607.07</v>
-      </c>
-      <c r="L7" s="3">
+        <v>9763484051005.2754</v>
+      </c>
+      <c r="L7" s="39">
         <f>Commercial_calculation!L9</f>
-        <v>69503651357609.383</v>
-      </c>
-      <c r="M7" s="3">
+        <v>10202840833300.512</v>
+      </c>
+      <c r="M7" s="39">
         <f>Commercial_calculation!M9</f>
-        <v>72631315668701.797</v>
-      </c>
-      <c r="N7" s="3">
+        <v>10661968670799.033</v>
+      </c>
+      <c r="N7" s="39">
         <f>Commercial_calculation!N9</f>
-        <v>75899724873793.375</v>
-      </c>
-      <c r="O7" s="3">
+        <v>11141757260984.988</v>
+      </c>
+      <c r="O7" s="39">
         <f>Commercial_calculation!O9</f>
-        <v>79315212493114.078</v>
-      </c>
-      <c r="P7" s="3">
+        <v>11643136337729.313</v>
+      </c>
+      <c r="P7" s="39">
         <f>Commercial_calculation!P9</f>
-        <v>82884397055304.203</v>
-      </c>
-      <c r="Q7" s="3">
+        <v>12167077472927.131</v>
+      </c>
+      <c r="Q7" s="39">
         <f>Commercial_calculation!Q9</f>
-        <v>86614194922792.891</v>
-      </c>
-      <c r="R7" s="3">
+        <v>12714595959208.852</v>
+      </c>
+      <c r="R7" s="39">
         <f>Commercial_calculation!R9</f>
-        <v>90511833694318.563</v>
-      </c>
-      <c r="S7" s="3">
+        <v>13286752777373.248</v>
+      </c>
+      <c r="S7" s="39">
         <f>Commercial_calculation!S9</f>
-        <v>94584866210562.891</v>
-      </c>
-      <c r="T7" s="3">
+        <v>13884656652355.043</v>
+      </c>
+      <c r="T7" s="39">
         <f>Commercial_calculation!T9</f>
-        <v>98841185190038.219</v>
-      </c>
-      <c r="U7" s="3">
+        <v>14509466201711.02</v>
+      </c>
+      <c r="U7" s="39">
         <f>Commercial_calculation!U9</f>
-        <v>103289038523589.94</v>
-      </c>
-      <c r="V7" s="3">
+        <v>15162392180788.014</v>
+      </c>
+      <c r="V7" s="39">
         <f>Commercial_calculation!V9</f>
-        <v>107937045257151.48</v>
-      </c>
-      <c r="W7" s="3">
+        <v>15844699828923.473</v>
+      </c>
+      <c r="W7" s="39">
         <f>Commercial_calculation!W9</f>
-        <v>112794212293723.3</v>
-      </c>
-      <c r="X7" s="3">
+        <v>16557711321225.027</v>
+      </c>
+      <c r="X7" s="39">
         <f>Commercial_calculation!X9</f>
-        <v>117869951846940.84</v>
-      </c>
-      <c r="Y7" s="3">
+        <v>17302808330680.152</v>
+      </c>
+      <c r="Y7" s="39">
         <f>Commercial_calculation!Y9</f>
-        <v>123174099680053.17</v>
-      </c>
-      <c r="Z7" s="3">
+        <v>18081434705560.758</v>
+      </c>
+      <c r="Z7" s="39">
         <f>Commercial_calculation!Z9</f>
-        <v>128716934165655.56</v>
-      </c>
-      <c r="AA7" s="3">
+        <v>18895099267310.992</v>
+      </c>
+      <c r="AA7" s="39">
         <f>Commercial_calculation!AA9</f>
-        <v>134509196203110.05</v>
-      </c>
-      <c r="AB7" s="3">
+        <v>19745378734339.984</v>
+      </c>
+      <c r="AB7" s="39">
         <f>Commercial_calculation!AB9</f>
-        <v>140562110032249.98</v>
-      </c>
-      <c r="AC7" s="3">
+        <v>20633920777385.281</v>
+      </c>
+      <c r="AC7" s="39">
         <f>Commercial_calculation!AC9</f>
-        <v>146887404983701.22</v>
-      </c>
-      <c r="AD7" s="3">
+        <v>21562447212367.617</v>
+      </c>
+      <c r="AD7" s="39">
         <f>Commercial_calculation!AD9</f>
-        <v>153497338207967.75</v>
-      </c>
-      <c r="AE7" s="3">
+        <v>22532757336924.16</v>
+      </c>
+      <c r="AE7" s="39">
         <f>Commercial_calculation!AE9</f>
-        <v>160404718427326.28</v>
-      </c>
-      <c r="AF7" s="3">
+        <v>23546731417085.746</v>
+      </c>
+      <c r="AF7" s="39">
         <f>Commercial_calculation!AF9</f>
-        <v>167622930756555.94</v>
-      </c>
-      <c r="AG7" s="3">
+        <v>24606334330854.602</v>
+      </c>
+      <c r="AG7" s="39">
         <f>Commercial_calculation!AG9</f>
-        <v>175165962640600.94</v>
+        <v>25713619375743.059</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
@@ -27225,6 +29660,7 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -34180,46 +36616,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="I1" s="16">
         <v>2020</v>
       </c>
       <c r="J1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -34251,7 +36687,7 @@
         <v>67518903420123.07</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="2">
         <v>128085531122407</v>
@@ -34301,7 +36737,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -34351,7 +36787,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J4" s="2">
         <v>58150486891512.766</v>
@@ -34401,7 +36837,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J5" s="2">
         <v>1635011946079.1394</v>
@@ -34451,7 +36887,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="2">
         <v>14511153872761.668</v>
@@ -34476,9 +36912,9 @@
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="43">
         <f t="shared" si="5"/>
-        <v>45560446860313.336</v>
+        <v>6688080101261.1963</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
@@ -34501,10 +36937,10 @@
         <v>148164054830.28726</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45560446860313.336</v>
+        <v>119</v>
+      </c>
+      <c r="J7" s="43">
+        <v>6688080101261.1963</v>
       </c>
       <c r="K7" s="2">
         <v>222246082245.43088</v>
@@ -34551,7 +36987,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J8" s="2">
         <v>29616860228748.609</v>
@@ -34601,7 +37037,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="2">
         <v>3658245906752.4121</v>
@@ -34651,7 +37087,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2">
         <v>17835815247411.25</v>
@@ -34701,7 +37137,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -34727,46 +37163,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I13" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="N13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="O13" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -34798,7 +37234,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J14" s="2">
         <v>17595574230689.395</v>
@@ -34844,7 +37280,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2">
         <v>11428732800000.002</v>
@@ -34884,7 +37320,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" s="2">
         <v>339009213195426.94</v>
@@ -34926,7 +37362,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -34964,7 +37400,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J18" s="2">
         <v>86945672100000.016</v>
@@ -35004,7 +37440,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="2">
         <v>18214542900000</v>
@@ -35044,7 +37480,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -35082,7 +37518,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="2">
         <v>87546310183815.938</v>
@@ -35122,7 +37558,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J22" s="2">
         <v>22005720583502.262</v>
@@ -35164,7 +37600,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -35175,25 +37611,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -35504,46 +37940,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="I1" s="16">
         <v>2021</v>
       </c>
       <c r="J1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -35575,7 +38011,7 @@
         <v>68119493654016.609</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="2">
         <v>129221921053730.27</v>
@@ -35625,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -35675,7 +38111,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J4" s="2">
         <v>57974902110890.578</v>
@@ -35725,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J5" s="2">
         <v>1609349044937.332</v>
@@ -35775,7 +38211,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="2">
         <v>14617592654224.467</v>
@@ -35802,7 +38238,7 @@
       </c>
       <c r="B7" s="2">
         <f t="shared" si="1"/>
-        <v>48873933904699.766</v>
+        <v>7174485926807.4648</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
@@ -35825,10 +38261,10 @@
         <v>158939622454.30817</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="2">
-        <v>48873933904699.766</v>
+        <v>119</v>
+      </c>
+      <c r="J7" s="43">
+        <v>7174485926807.4648</v>
       </c>
       <c r="K7" s="2">
         <v>238409433681.46222</v>
@@ -35875,7 +38311,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J8" s="2">
         <v>29151998453271.219</v>
@@ -35925,7 +38361,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="2">
         <v>3600826630225.0806</v>
@@ -35975,7 +38411,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2">
         <v>17555866978791.26</v>
@@ -36025,7 +38461,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -36051,46 +38487,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I13" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="N13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="O13" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -36122,7 +38558,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J14" s="2">
         <v>19482237708106.813</v>
@@ -36170,7 +38606,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2">
         <v>7857253800000</v>
@@ -36210,7 +38646,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" s="2">
         <v>355852532026135.06</v>
@@ -36252,7 +38688,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -36290,7 +38726,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J18" s="2">
         <v>95429070691603.063</v>
@@ -36330,7 +38766,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="2">
         <v>26613557282608.699</v>
@@ -36370,7 +38806,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -36408,7 +38844,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="2">
         <v>87387019904385.5</v>
@@ -36448,7 +38884,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J22" s="2">
         <v>21965681233203.488</v>
@@ -36490,7 +38926,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -36504,25 +38940,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="I25"/>
     </row>
@@ -36834,10 +39270,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -36922,15 +39358,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="37">
         <v>-0.01</v>
@@ -36938,7 +39374,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="37">
         <v>2.5000000000000001E-2</v>
@@ -36946,7 +39382,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
@@ -36954,7 +39390,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="37">
         <v>-6.0000000000000001E-3</v>
@@ -36962,7 +39398,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="37">
         <v>7.0000000000000001E-3</v>
@@ -36970,7 +39406,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="37">
         <v>-1.4E-2</v>
@@ -36978,10 +39414,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -37000,10 +39436,10 @@
         <v>-8.6999999999999994E-2</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -37034,7 +39470,7 @@
       <c r="A28" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="42">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
@@ -37092,31 +39528,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -37310,7 +39746,7 @@
       </c>
       <c r="B7" s="2">
         <f>Commercial_calculation!W9</f>
-        <v>112794212293723.3</v>
+        <v>16557711321225.027</v>
       </c>
       <c r="C7" s="2">
         <f>Commercial_calculation!W21</f>
@@ -37334,11 +39770,11 @@
       </c>
       <c r="I7" s="2">
         <f t="shared" si="0"/>
-        <v>140488401003239.09</v>
+        <v>44251900030740.813</v>
       </c>
       <c r="J7" s="18">
         <f>I7/10^6/About!$B$30/10^6</f>
-        <v>3.540257716842663</v>
+        <v>1.1151321351089207</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -37493,11 +39929,11 @@
       <c r="A12" s="16"/>
       <c r="I12" s="2">
         <f>SUM(I2:I11)</f>
-        <v>1078632810520066.5</v>
+        <v>982396309547568.13</v>
       </c>
       <c r="J12" s="18">
         <f>I12/10^6/About!$B$30/10^6</f>
-        <v>27.181163027083731</v>
+        <v>24.756037445349985</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -37506,31 +39942,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -37918,31 +40354,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="F27" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="G27" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>42</v>
-      </c>
       <c r="I27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -38379,7 +40815,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -38400,126 +40836,126 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="K1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="S1" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="V1" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="W1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="X1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="AA1" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB1" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" s="20" t="s">
+      <c r="AC1" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" s="20" t="s">
+      <c r="AD1" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AD1" s="20" t="s">
+      <c r="AE1" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AE1" s="20" t="s">
+      <c r="AF1" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AF1" s="20" t="s">
+      <c r="AG1" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="AG1" s="20" t="s">
+      <c r="AH1" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="AH1" s="20" t="s">
+      <c r="AI1" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="AI1" s="20" t="s">
+      <c r="AJ1" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="AJ1" s="20" t="s">
+      <c r="AK1" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AK1" s="30" t="s">
+      <c r="AL1" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="AL1" s="30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="C2" s="21">
         <v>3574</v>
@@ -38634,10 +41070,10 @@
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C3" s="21">
         <v>1976</v>
@@ -38752,10 +41188,10 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="21">
         <v>46</v>
@@ -38870,10 +41306,10 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C5" s="21">
         <v>0</v>
@@ -38986,10 +41422,10 @@
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="21">
         <v>520</v>
@@ -39104,10 +41540,10 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C7" s="21">
         <v>230</v>
@@ -39222,10 +41658,10 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="21">
         <v>1996</v>
@@ -39340,10 +41776,10 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C9" s="21">
         <v>486</v>
@@ -39458,10 +41894,10 @@
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="21">
         <v>537</v>
@@ -39576,10 +42012,10 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C11" s="21">
         <v>1191</v>
@@ -39694,10 +42130,10 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="21">
         <v>436</v>
@@ -39812,10 +42248,10 @@
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C13" s="21">
         <v>55</v>
@@ -39930,10 +42366,10 @@
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="21">
         <v>40</v>
@@ -40048,10 +42484,10 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="C15" s="21">
         <v>14</v>
@@ -40166,10 +42602,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="C17" s="26">
         <v>2019</v>
@@ -40181,13 +42617,13 @@
         <v>2021</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="I17" s="29">
         <v>2019</v>
@@ -40199,15 +42635,15 @@
         <v>2021</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="C18" s="18">
         <f>SUM(C2:N2)</f>
@@ -40222,10 +42658,10 @@
         <v>23704.455724820378</v>
       </c>
       <c r="G18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="I18" s="32">
         <f>C18*About!$B$30*10^9</f>
@@ -40242,10 +42678,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C19" s="18">
         <f>SUM(C3:N3)+B42</f>
@@ -40260,10 +42696,10 @@
         <v>22760.5431348325</v>
       </c>
       <c r="G19" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I19" s="32">
         <f>C19*About!$B$30*10^9</f>
@@ -40280,10 +42716,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="18">
         <f t="shared" ref="C20:D30" si="11">SUM(C4:N4)</f>
@@ -40298,10 +42734,10 @@
         <v>198</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I20" s="32">
         <f>C20*About!$B$30*10^9</f>
@@ -40318,10 +42754,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C21" s="18">
         <f t="shared" si="11"/>
@@ -40336,10 +42772,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I21" s="32">
         <f>C21*About!$B$30*10^9</f>
@@ -40356,10 +42792,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="18">
         <f t="shared" si="11"/>
@@ -40374,10 +42810,10 @@
         <v>2871.7653061224491</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="32">
         <f>C22*About!$B$30*10^9</f>
@@ -40394,10 +42830,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C23" s="18">
         <f>SUM(C7:N7)+B43</f>
@@ -40412,10 +42848,10 @@
         <v>2821.7816091954023</v>
       </c>
       <c r="G23" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I23" s="32">
         <f>C23*About!$B$30*10^9</f>
@@ -40432,10 +42868,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="18">
         <f t="shared" si="11"/>
@@ -40450,10 +42886,10 @@
         <v>10848.48368522073</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="32">
         <f>C24*About!$B$30*10^9</f>
@@ -40470,10 +42906,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C25" s="18">
         <f>SUM(C9:N9)+B44</f>
@@ -40488,10 +42924,10 @@
         <v>3632.3333333333335</v>
       </c>
       <c r="G25" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I25" s="32">
         <f>C25*About!$B$30*10^9</f>
@@ -40508,10 +42944,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="18">
         <f t="shared" si="11"/>
@@ -40526,10 +42962,10 @@
         <v>6709.7759336099589</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" s="32">
         <f>C26*About!$B$30*10^9</f>
@@ -40546,10 +42982,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C27" s="18">
         <f>SUM(C11:N11)+B45</f>
@@ -40564,10 +43000,10 @@
         <v>14369.366336633662</v>
       </c>
       <c r="G27" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I27" s="32">
         <f>C27*About!$B$30*10^9</f>
@@ -40584,10 +43020,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" s="18">
         <f t="shared" si="11"/>
@@ -40602,10 +43038,10 @@
         <v>2404.7786259541986</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I28" s="32">
         <f>C28*About!$B$30*10^9</f>
@@ -40622,10 +43058,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C29" s="18">
         <f>SUM(C13:N13)+B46</f>
@@ -40640,10 +43076,10 @@
         <v>412</v>
       </c>
       <c r="G29" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I29" s="32">
         <f>C29*About!$B$30*10^9</f>
@@ -40660,10 +43096,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="18">
         <f t="shared" si="11"/>
@@ -40678,10 +43114,10 @@
         <v>670.6521739130435</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I30" s="32">
         <f>C30*About!$B$30*10^9</f>
@@ -40698,10 +43134,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="C31" s="18">
         <f>SUM(C15:N15)+B47</f>
@@ -40716,10 +43152,10 @@
         <v>1534.0618556701031</v>
       </c>
       <c r="G31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="I31" s="32">
         <f>C31*About!$B$30*10^9</f>
@@ -40736,120 +43172,120 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="D33" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="E33" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="F33" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="G33" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="H33" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="I33" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="J33" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="K33" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="L33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="L33" s="20" t="s">
+      <c r="M33" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="M33" s="20" t="s">
+      <c r="N33" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="N33" s="20" t="s">
+      <c r="O33" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="O33" s="20" t="s">
+      <c r="P33" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="P33" s="20" t="s">
+      <c r="Q33" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="Q33" s="20" t="s">
+      <c r="R33" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="R33" s="20" t="s">
+      <c r="S33" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="S33" s="20" t="s">
+      <c r="T33" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="T33" s="20" t="s">
+      <c r="U33" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="20" t="s">
+      <c r="V33" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="V33" s="20" t="s">
+      <c r="W33" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="W33" s="20" t="s">
+      <c r="X33" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="X33" s="20" t="s">
+      <c r="Y33" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="Y33" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="Z33" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA33" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AA33" s="20" t="s">
+      <c r="AB33" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AB33" s="20" t="s">
+      <c r="AC33" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AC33" s="20" t="s">
+      <c r="AD33" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AD33" s="20" t="s">
+      <c r="AE33" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AE33" s="20" t="s">
+      <c r="AF33" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="AF33" s="20" t="s">
+      <c r="AG33" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="AG33" s="20" t="s">
+      <c r="AH33" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="AH33" s="20" t="s">
+      <c r="AI33" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="AI33" s="20" t="s">
+      <c r="AJ33" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AJ33" s="30" t="s">
+      <c r="AK33" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="AK33" s="30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="21">
         <v>579</v>
@@ -40964,7 +43400,7 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="21">
         <v>163</v>
@@ -41079,7 +43515,7 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="21">
         <v>14</v>
@@ -41194,7 +43630,7 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" s="21">
         <v>271</v>
@@ -41309,7 +43745,7 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="21">
         <v>13</v>
@@ -41424,7 +43860,7 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" s="21">
         <v>118</v>
@@ -41539,7 +43975,7 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="26">
         <v>2019</v>
@@ -41551,10 +43987,10 @@
         <v>2021</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="26">
         <v>2019</v>
@@ -41566,12 +44002,12 @@
         <v>2021</v>
       </c>
       <c r="K41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B42" s="27">
         <f t="shared" ref="B42:B47" si="14">SUM(B34:M34)</f>
@@ -41586,7 +44022,7 @@
         <v>5502.5431348325019</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" s="28">
         <f>B42*About!$B$30*10^9</f>
@@ -41603,7 +44039,7 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="27">
         <f t="shared" si="14"/>
@@ -41618,7 +44054,7 @@
         <v>1105.7816091954023</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H43" s="28">
         <f>B43*About!$B$30*10^9</f>
@@ -41635,7 +44071,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="27">
         <f t="shared" si="14"/>
@@ -41650,7 +44086,7 @@
         <v>90.333333333333343</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" s="28">
         <f>B44*About!$B$30*10^9</f>
@@ -41667,7 +44103,7 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B45" s="27">
         <f t="shared" si="14"/>
@@ -41682,7 +44118,7 @@
         <v>2842.3663366336632</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H45" s="28">
         <f>B45*About!$B$30*10^9</f>
@@ -41699,7 +44135,7 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" s="27">
         <f t="shared" si="14"/>
@@ -41714,7 +44150,7 @@
         <v>70</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" s="28">
         <f>B46*About!$B$30*10^9</f>
@@ -41731,7 +44167,7 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="27">
         <f t="shared" si="14"/>
@@ -41746,7 +44182,7 @@
         <v>1395.0618556701031</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47" s="28">
         <f>B47*About!$B$30*10^9</f>
@@ -41779,12 +44215,16 @@
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="E2">
+        <f>1+Forecast!$B28</f>
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -42549,136 +44989,136 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
         <f>INDEX(SYCEU!$B$2:$G$11, MATCH($A9, SYCEU!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, SYCEU!$B$1:$G$1, 0))</f>
-        <v>42700000000000</v>
+        <v>6267151983000.002</v>
       </c>
       <c r="C9" s="2">
         <f>INDEX('2020'!$B$2:$G$11, MATCH($A9, '2020'!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, '2020'!$B$1:$G$1, 0))</f>
-        <v>45560446860313.336</v>
+        <v>6688080101261.1963</v>
       </c>
       <c r="D9" s="2">
         <f>INDEX('2021'!$B$2:$G$11, MATCH($A9, '2021'!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, '2021'!$B$1:$G$1, 0))</f>
-        <v>48873933904699.766</v>
+        <v>7174485926807.4648</v>
       </c>
       <c r="E9" s="2">
         <f>MAX(0,D9*(1+Forecast!$B28))</f>
-        <v>51073260930411.25</v>
+        <v>7497337793513.7998</v>
       </c>
       <c r="F9" s="2">
         <f>MAX(0,E9*(1+Forecast!$B28))</f>
-        <v>53371557672279.75</v>
+        <v>7834717994221.9199</v>
       </c>
       <c r="G9" s="2">
         <f>MAX(0,F9*(1+Forecast!$B28))</f>
-        <v>55773277767532.336</v>
+        <v>8187280303961.9063</v>
       </c>
       <c r="H9" s="2">
         <f>MAX(0,G9*(1+Forecast!$B28))</f>
-        <v>58283075267071.289</v>
+        <v>8555707917640.1914</v>
       </c>
       <c r="I9" s="2">
         <f>MAX(0,H9*(1+Forecast!$B28))</f>
-        <v>60905813654089.492</v>
+        <v>8940714773934</v>
       </c>
       <c r="J9" s="2">
         <f>MAX(0,I9*(1+Forecast!$B28))</f>
-        <v>63646575268523.516</v>
+        <v>9343046938761.0293</v>
       </c>
       <c r="K9" s="2">
         <f>MAX(0,J9*(1+Forecast!$B28))</f>
-        <v>66510671155607.07</v>
+        <v>9763484051005.2754</v>
       </c>
       <c r="L9" s="2">
         <f>MAX(0,K9*(1+Forecast!$B28))</f>
-        <v>69503651357609.383</v>
+        <v>10202840833300.512</v>
       </c>
       <c r="M9" s="2">
         <f>MAX(0,L9*(1+Forecast!$B28))</f>
-        <v>72631315668701.797</v>
+        <v>10661968670799.033</v>
       </c>
       <c r="N9" s="2">
         <f>MAX(0,M9*(1+Forecast!$B28))</f>
-        <v>75899724873793.375</v>
+        <v>11141757260984.988</v>
       </c>
       <c r="O9" s="2">
         <f>MAX(0,N9*(1+Forecast!$B28))</f>
-        <v>79315212493114.078</v>
+        <v>11643136337729.313</v>
       </c>
       <c r="P9" s="2">
         <f>MAX(0,O9*(1+Forecast!$B28))</f>
-        <v>82884397055304.203</v>
+        <v>12167077472927.131</v>
       </c>
       <c r="Q9" s="2">
         <f>MAX(0,P9*(1+Forecast!$B28))</f>
-        <v>86614194922792.891</v>
+        <v>12714595959208.852</v>
       </c>
       <c r="R9" s="2">
         <f>MAX(0,Q9*(1+Forecast!$B28))</f>
-        <v>90511833694318.563</v>
+        <v>13286752777373.248</v>
       </c>
       <c r="S9" s="2">
         <f>MAX(0,R9*(1+Forecast!$B28))</f>
-        <v>94584866210562.891</v>
+        <v>13884656652355.043</v>
       </c>
       <c r="T9" s="2">
         <f>MAX(0,S9*(1+Forecast!$B28))</f>
-        <v>98841185190038.219</v>
+        <v>14509466201711.02</v>
       </c>
       <c r="U9" s="2">
         <f>MAX(0,T9*(1+Forecast!$B28))</f>
-        <v>103289038523589.94</v>
+        <v>15162392180788.014</v>
       </c>
       <c r="V9" s="2">
         <f>MAX(0,U9*(1+Forecast!$B28))</f>
-        <v>107937045257151.48</v>
+        <v>15844699828923.473</v>
       </c>
       <c r="W9" s="2">
         <f>MAX(0,V9*(1+Forecast!$B28))</f>
-        <v>112794212293723.3</v>
+        <v>16557711321225.027</v>
       </c>
       <c r="X9" s="2">
         <f>MAX(0,W9*(1+Forecast!$B28))</f>
-        <v>117869951846940.84</v>
+        <v>17302808330680.152</v>
       </c>
       <c r="Y9" s="2">
         <f>MAX(0,X9*(1+Forecast!$B28))</f>
-        <v>123174099680053.17</v>
+        <v>18081434705560.758</v>
       </c>
       <c r="Z9" s="2">
         <f>MAX(0,Y9*(1+Forecast!$B28))</f>
-        <v>128716934165655.56</v>
+        <v>18895099267310.992</v>
       </c>
       <c r="AA9" s="2">
         <f>MAX(0,Z9*(1+Forecast!$B28))</f>
-        <v>134509196203110.05</v>
+        <v>19745378734339.984</v>
       </c>
       <c r="AB9" s="2">
         <f>MAX(0,AA9*(1+Forecast!$B28))</f>
-        <v>140562110032249.98</v>
+        <v>20633920777385.281</v>
       </c>
       <c r="AC9" s="2">
         <f>MAX(0,AB9*(1+Forecast!$B28))</f>
-        <v>146887404983701.22</v>
+        <v>21562447212367.617</v>
       </c>
       <c r="AD9" s="2">
         <f>MAX(0,AC9*(1+Forecast!$B28))</f>
-        <v>153497338207967.75</v>
+        <v>22532757336924.16</v>
       </c>
       <c r="AE9" s="2">
         <f>MAX(0,AD9*(1+Forecast!$B28))</f>
-        <v>160404718427326.28</v>
+        <v>23546731417085.746</v>
       </c>
       <c r="AF9" s="2">
         <f>MAX(0,AE9*(1+Forecast!$B28))</f>
-        <v>167622930756555.94</v>
+        <v>24606334330854.602</v>
       </c>
       <c r="AG9" s="2">
         <f>MAX(0,AF9*(1+Forecast!$B28))</f>
-        <v>175165962640600.94</v>
+        <v>25713619375743.059</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -43215,7 +45655,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -44646,7 +47086,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -46077,7 +48517,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -47508,7 +49948,7 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -48939,7 +51379,7 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -50385,12 +52825,12 @@
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -51821,7 +54261,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -53252,7 +55692,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -54683,7 +57123,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -56114,7 +58554,7 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -57545,7 +59985,7 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -58978,175 +61418,4 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44067CE8-66FC-4A82-9FEE-D70C99A00400}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6140F724-F8FB-439D-89B3-32751B1C3108}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA998932-B428-4066-9723-C265089B8E0B}"/>
 </file>